--- a/artfynd/A 18084-2026 artfynd.xlsx
+++ b/artfynd/A 18084-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1924110</v>
+        <v>91669</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634061.9827100541</v>
+        <v>634199</v>
       </c>
       <c r="R2" t="n">
-        <v>7012449.615098675</v>
+        <v>7012440</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>glänta i granskog</t>
+          <t>bäckmiljö</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1549217</v>
+        <v>235996</v>
       </c>
       <c r="B3" t="n">
-        <v>89409</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634213.9396978561</v>
+        <v>634213</v>
       </c>
       <c r="R3" t="n">
-        <v>7012437.876547346</v>
+        <v>7012465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,21 +857,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,7 +873,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>bäckmiljö</t>
+          <t>ogallrad äldre fuktig granskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -911,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # levande gran</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1924123</v>
+        <v>236011</v>
       </c>
       <c r="B4" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633836.1485615228</v>
+        <v>634193</v>
       </c>
       <c r="R4" t="n">
-        <v>7012520.15065083</v>
+        <v>7012646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,21 +971,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1032,7 +987,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>ljus blockig granblandskog</t>
+          <t>äldre granskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1040,7 +995,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # sälg</t>
+          <t>1 substratenheter # grov gammal granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91669</v>
+        <v>316090</v>
       </c>
       <c r="B5" t="n">
-        <v>94120</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634198.9133261386</v>
+        <v>634223</v>
       </c>
       <c r="R5" t="n">
-        <v>7012440.411721786</v>
+        <v>7012647</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,21 +1085,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>bäckmiljö</t>
+          <t>skiktad äldre granskog</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1194,12 +1134,7 @@
         <v>316772</v>
       </c>
       <c r="B6" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634238.4044465699</v>
+        <v>634238</v>
       </c>
       <c r="R6" t="n">
-        <v>7012404.127204975</v>
+        <v>7012404</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1264,19 +1199,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,15 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>316090</v>
+        <v>1924110</v>
       </c>
       <c r="B7" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1360,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634223.3238876781</v>
+        <v>634062</v>
       </c>
       <c r="R7" t="n">
-        <v>7012646.866902879</v>
+        <v>7012450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,21 +1313,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1419,7 +1329,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>skiktad äldre granskog</t>
+          <t>glänta i granskog</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1427,7 +1337,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # gammal sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1449,15 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>236011</v>
+        <v>1924123</v>
       </c>
       <c r="B8" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,21 +1370,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1489,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634192.6330825549</v>
+        <v>633836</v>
       </c>
       <c r="R8" t="n">
-        <v>7012645.58917202</v>
+        <v>7012520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,21 +1427,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1548,7 +1443,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>äldre granskog</t>
+          <t>ljus blockig granblandskog</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1556,7 +1451,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal granlåga</t>
+          <t>1 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1578,15 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>235996</v>
+        <v>316091</v>
       </c>
       <c r="B9" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1618,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>634212.8138011254</v>
+        <v>634507</v>
       </c>
       <c r="R9" t="n">
-        <v>7012464.92129453</v>
+        <v>7011864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,21 +1541,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1677,7 +1557,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>ogallrad äldre fuktig granskog</t>
+          <t>asprik granskog</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1707,15 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>316091</v>
+        <v>1924339</v>
       </c>
       <c r="B10" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,21 +1598,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1747,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>634507.3412868382</v>
+        <v>634441</v>
       </c>
       <c r="R10" t="n">
-        <v>7011864.415913994</v>
+        <v>7012014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1780,21 +1655,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1806,15 +1671,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>asprik granskog</t>
+          <t>gles granblandskog</t>
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>2 substratenheter # gammal sälg</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1836,15 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1924596</v>
+        <v>1924349</v>
       </c>
       <c r="B11" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1876,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>634440.5132209717</v>
+        <v>634312</v>
       </c>
       <c r="R11" t="n">
-        <v>7012013.818716696</v>
+        <v>7011797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1909,21 +1769,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1933,17 +1783,12 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>gles granblandskog</t>
-        </is>
-      </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>2 substratenheter # gammal sälg</t>
+          <t>3 substratenheter # gammal rönn o sälg</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1968,12 +1813,7 @@
         <v>1924353</v>
       </c>
       <c r="B12" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>634506.2691509414</v>
+        <v>634506</v>
       </c>
       <c r="R12" t="n">
-        <v>7011868.43570243</v>
+        <v>7011868</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,19 +1878,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2097,12 +1927,7 @@
         <v>1933192</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2134,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>634435.3968545439</v>
+        <v>634435</v>
       </c>
       <c r="R13" t="n">
-        <v>7012006.379937201</v>
+        <v>7012006</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,19 +1992,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2223,37 +2038,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1924349</v>
+        <v>3027862</v>
       </c>
       <c r="B14" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2263,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>634312.0679332522</v>
+        <v>634522</v>
       </c>
       <c r="R14" t="n">
-        <v>7011797.114909112</v>
+        <v>7011906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2296,21 +2106,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2320,12 +2120,9 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AN14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>3 substratenheter # gammal rönn o sälg</t>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>blockig, mossig granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2347,37 +2144,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3027862</v>
+        <v>142802</v>
       </c>
       <c r="B15" t="n">
-        <v>96333</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2387,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634521.9006538398</v>
+        <v>634496</v>
       </c>
       <c r="R15" t="n">
-        <v>7011905.668133405</v>
+        <v>7011639</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2420,21 +2212,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2446,7 +2228,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>blockig, mossig granskog</t>
+          <t>asprik granskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # halvgrov granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2468,37 +2258,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>400188</v>
+        <v>236021</v>
       </c>
       <c r="B16" t="n">
-        <v>94436</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>990</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2508,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634349.2555709549</v>
+        <v>634364</v>
       </c>
       <c r="R16" t="n">
-        <v>7011783.760542322</v>
+        <v>7011788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2541,21 +2326,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2564,18 +2339,13 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>luckig granskog</t>
-        </is>
       </c>
       <c r="AN16" t="n">
         <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal granlåga</t>
+          <t>1 substratenheter # grov granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2597,37 +2367,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>236021</v>
+        <v>400188</v>
       </c>
       <c r="B17" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2637,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>634364.47358996</v>
+        <v>634349</v>
       </c>
       <c r="R17" t="n">
-        <v>7011787.555944956</v>
+        <v>7011784</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2670,21 +2435,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2693,13 +2448,18 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>luckig granskog</t>
+        </is>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov granlåga</t>
+          <t>1 substratenheter # gammal granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2721,37 +2481,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>384830</v>
+        <v>316743</v>
       </c>
       <c r="B18" t="n">
-        <v>89831</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2761,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>634369.4020324992</v>
+        <v>634366</v>
       </c>
       <c r="R18" t="n">
-        <v>7011788.664544546</v>
+        <v>7011778</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2794,21 +2549,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2817,6 +2562,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>asprik,luckig granskog</t>
+        </is>
       </c>
       <c r="AN18" t="n">
         <v>1</v>
@@ -2845,37 +2595,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1886489</v>
+        <v>384830</v>
       </c>
       <c r="B19" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2885,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>634394.2545361024</v>
+        <v>634369</v>
       </c>
       <c r="R19" t="n">
-        <v>7011485.293123349</v>
+        <v>7011789</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2918,21 +2663,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2941,18 +2676,13 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>medelålders granskog</t>
-        </is>
       </c>
       <c r="AN19" t="n">
         <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # asp</t>
+          <t>1 substratenheter # grov granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2974,15 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>236245</v>
+        <v>1924355</v>
       </c>
       <c r="B20" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2990,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3014,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>634406.4882418221</v>
+        <v>634468</v>
       </c>
       <c r="R20" t="n">
-        <v>7011604.136704877</v>
+        <v>7011651</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3047,21 +2772,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3071,17 +2786,12 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>olikåldrig granskog</t>
-        </is>
-      </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # halvgrov granlåga</t>
+          <t>5 substratenheter # asp</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3103,37 +2813,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>384813</v>
+        <v>236245</v>
       </c>
       <c r="B21" t="n">
-        <v>89831</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3143,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>634221.2555221713</v>
+        <v>634406</v>
       </c>
       <c r="R21" t="n">
-        <v>7011479.895327163</v>
+        <v>7011604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,21 +2881,11 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2008-09-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3202,7 +2897,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>bäckdal m granskog och al</t>
+          <t>olikåldrig granskog</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -3210,7 +2905,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # halvgrov granlåga</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3225,6 +2920,348 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr">
+        <is>
+          <t>Skogsbruksplan Björkå bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>384813</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björkå bruks skogsmark, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>634221</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7011480</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2008-09-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2008-09-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>bäckdal m granskog och al</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Skogsbruksplan Björkå bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>385085</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Björkå bruks skogsmark, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>634473</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7011623</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2008-09-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2008-09-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>asprik, luckig granskog</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>3 substratenheter # granlåga</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Skogsbruksplan Björkå bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1886489</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Björkå bruks skogsmark, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>634394</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011485</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2008-09-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2008-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>medelålders granskog</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>1 substratenheter # asp</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Skogsbruksplan Björkå bruk</t>
         </is>

--- a/artfynd/A 18084-2026 artfynd.xlsx
+++ b/artfynd/A 18084-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91669</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/235996</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236011</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316090</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316772</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1924110</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1924123</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1924349</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316091</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1924339</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1924353</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2035,6 +2095,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1933192</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2141,6 +2206,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3027862</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236021</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2364,6 +2439,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/400188</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2478,6 +2558,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316743</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2587,6 +2672,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/384830</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2701,6 +2791,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/142802</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2810,6 +2905,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1924355</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2924,6 +3024,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/384813</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3038,6 +3143,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236245</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3152,6 +3262,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/385085</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3266,8 +3381,38 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1886489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>